--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Stat.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Stat.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="1205">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -2429,6 +2429,30 @@
   </si>
   <si>
     <t xml:space="preserve">テレキネシスの影響を受けにくくなる状態。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시간 정지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Stop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">時止め</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시간이 정지해서 움직일 수 없게 되는 상태.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A condition where time is frozen and you are unable to act.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">時間が停止し動けなくなる状態。</t>
   </si>
   <si>
     <t xml:space="preserve">50</t>
@@ -3888,7 +3912,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T105"/>
+  <dimension ref="A1:T106"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="1" style="0" width="16.15"/>
@@ -7217,748 +7241,748 @@
         <v>799</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>428</v>
+        <v>800</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D68" s="0" t="s">
+        <v>802</v>
+      </c>
+      <c r="E68" s="0" t="s">
+        <v>803</v>
+      </c>
+      <c r="F68" s="0" t="s">
+        <v>804</v>
+      </c>
+      <c r="G68" s="0" t="s">
+        <v>805</v>
+      </c>
+      <c r="H68" s="0" t="s">
+        <v>806</v>
+      </c>
+      <c r="I68" s="0" t="s">
         <v>801</v>
       </c>
-      <c r="E68" s="0" t="s">
+      <c r="J68" s="0" t="s">
         <v>802</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="K68" s="0" t="s">
         <v>803</v>
-      </c>
-      <c r="G68" s="0" t="s">
-        <v>804</v>
-      </c>
-      <c r="H68" s="0" t="s">
-        <v>805</v>
-      </c>
-      <c r="I68" s="0" t="s">
-        <v>800</v>
-      </c>
-      <c r="J68" s="0" t="s">
-        <v>801</v>
-      </c>
-      <c r="K68" s="0" t="s">
-        <v>802</v>
-      </c>
-      <c r="L68" s="0" t="s">
-        <v>806</v>
-      </c>
-      <c r="M68" s="0" t="s">
-        <v>807</v>
-      </c>
-      <c r="N68" s="0" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
+        <v>807</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>808</v>
+      </c>
+      <c r="D69" s="0" t="s">
         <v>809</v>
       </c>
-      <c r="B69" s="0" t="s">
-        <v>581</v>
-      </c>
-      <c r="C69" s="0" t="s">
+      <c r="E69" s="0" t="s">
         <v>810</v>
       </c>
-      <c r="D69" s="0" t="s">
+      <c r="F69" s="0" t="s">
         <v>811</v>
       </c>
-      <c r="E69" s="0" t="s">
+      <c r="G69" s="0" t="s">
         <v>812</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="H69" s="0" t="s">
         <v>813</v>
       </c>
-      <c r="G69" s="0" t="s">
+      <c r="I69" s="0" t="s">
+        <v>808</v>
+      </c>
+      <c r="J69" s="0" t="s">
+        <v>809</v>
+      </c>
+      <c r="K69" s="0" t="s">
+        <v>810</v>
+      </c>
+      <c r="L69" s="0" t="s">
         <v>814</v>
       </c>
-      <c r="H69" s="0" t="s">
+      <c r="M69" s="0" t="s">
         <v>815</v>
       </c>
-      <c r="I69" s="0" t="s">
-        <v>810</v>
-      </c>
-      <c r="J69" s="0" t="s">
-        <v>811</v>
-      </c>
-      <c r="K69" s="0" t="s">
-        <v>812</v>
-      </c>
-      <c r="L69" s="0" t="s">
+      <c r="N69" s="0" t="s">
         <v>816</v>
-      </c>
-      <c r="M69" s="0" t="s">
-        <v>817</v>
-      </c>
-      <c r="N69" s="0" t="s">
-        <v>818</v>
-      </c>
-      <c r="R69" s="0" t="s">
-        <v>819</v>
-      </c>
-      <c r="S69" s="0" t="s">
-        <v>820</v>
-      </c>
-      <c r="T69" s="0" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
+        <v>817</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>581</v>
+      </c>
+      <c r="C70" s="0" t="s">
+        <v>818</v>
+      </c>
+      <c r="D70" s="0" t="s">
+        <v>819</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>820</v>
+      </c>
+      <c r="F70" s="0" t="s">
+        <v>821</v>
+      </c>
+      <c r="G70" s="0" t="s">
         <v>822</v>
       </c>
-      <c r="B70" s="0" t="s">
-        <v>428</v>
-      </c>
-      <c r="C70" s="0" t="s">
+      <c r="H70" s="0" t="s">
         <v>823</v>
       </c>
-      <c r="D70" s="0" t="s">
+      <c r="I70" s="0" t="s">
+        <v>818</v>
+      </c>
+      <c r="J70" s="0" t="s">
+        <v>819</v>
+      </c>
+      <c r="K70" s="0" t="s">
+        <v>820</v>
+      </c>
+      <c r="L70" s="0" t="s">
         <v>824</v>
       </c>
-      <c r="E70" s="0" t="s">
+      <c r="M70" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="N70" s="0" t="s">
         <v>826</v>
       </c>
-      <c r="G70" s="0" t="s">
+      <c r="R70" s="0" t="s">
         <v>827</v>
       </c>
-      <c r="H70" s="0" t="s">
+      <c r="S70" s="0" t="s">
         <v>828</v>
       </c>
-      <c r="I70" s="0" t="s">
-        <v>823</v>
-      </c>
-      <c r="J70" s="0" t="s">
-        <v>824</v>
-      </c>
-      <c r="K70" s="0" t="s">
-        <v>825</v>
-      </c>
-      <c r="L70" s="0" t="s">
+      <c r="T70" s="0" t="s">
         <v>829</v>
-      </c>
-      <c r="M70" s="0" t="s">
-        <v>830</v>
-      </c>
-      <c r="N70" s="0" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B71" s="0" t="s">
         <v>428</v>
       </c>
       <c r="C71" s="0" t="s">
+        <v>831</v>
+      </c>
+      <c r="D71" s="0" t="s">
+        <v>832</v>
+      </c>
+      <c r="E71" s="0" t="s">
         <v>833</v>
       </c>
-      <c r="D71" s="0" t="s">
+      <c r="F71" s="0" t="s">
         <v>834</v>
       </c>
-      <c r="E71" s="0" t="s">
+      <c r="G71" s="0" t="s">
         <v>835</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="H71" s="0" t="s">
         <v>836</v>
       </c>
-      <c r="G71" s="0" t="s">
+      <c r="I71" s="0" t="s">
+        <v>831</v>
+      </c>
+      <c r="J71" s="0" t="s">
+        <v>832</v>
+      </c>
+      <c r="K71" s="0" t="s">
+        <v>833</v>
+      </c>
+      <c r="L71" s="0" t="s">
         <v>837</v>
       </c>
-      <c r="H71" s="0" t="s">
+      <c r="M71" s="0" t="s">
         <v>838</v>
       </c>
-      <c r="I71" s="0" t="s">
-        <v>833</v>
-      </c>
-      <c r="J71" s="0" t="s">
-        <v>834</v>
-      </c>
-      <c r="K71" s="0" t="s">
-        <v>835</v>
-      </c>
-      <c r="L71" s="0" t="s">
+      <c r="N71" s="0" t="s">
         <v>839</v>
-      </c>
-      <c r="M71" s="0" t="s">
-        <v>840</v>
-      </c>
-      <c r="N71" s="0" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="C72" s="0" t="s">
+        <v>841</v>
+      </c>
+      <c r="D72" s="0" t="s">
         <v>842</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="E72" s="0" t="s">
         <v>843</v>
       </c>
-      <c r="C72" s="0" t="s">
+      <c r="F72" s="0" t="s">
         <v>844</v>
       </c>
-      <c r="D72" s="0" t="s">
+      <c r="G72" s="0" t="s">
         <v>845</v>
       </c>
-      <c r="E72" s="0" t="s">
+      <c r="H72" s="0" t="s">
         <v>846</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="I72" s="0" t="s">
+        <v>841</v>
+      </c>
+      <c r="J72" s="0" t="s">
+        <v>842</v>
+      </c>
+      <c r="K72" s="0" t="s">
+        <v>843</v>
+      </c>
+      <c r="L72" s="0" t="s">
         <v>847</v>
       </c>
-      <c r="G72" s="0" t="s">
+      <c r="M72" s="0" t="s">
         <v>848</v>
       </c>
-      <c r="H72" s="0" t="s">
+      <c r="N72" s="0" t="s">
         <v>849</v>
-      </c>
-      <c r="I72" s="0" t="s">
-        <v>844</v>
-      </c>
-      <c r="J72" s="0" t="s">
-        <v>845</v>
-      </c>
-      <c r="K72" s="0" t="s">
-        <v>846</v>
-      </c>
-      <c r="L72" s="0" t="s">
-        <v>850</v>
-      </c>
-      <c r="M72" s="0" t="s">
-        <v>851</v>
-      </c>
-      <c r="N72" s="0" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
+        <v>850</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>851</v>
+      </c>
+      <c r="C73" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="D73" s="0" t="s">
         <v>853</v>
       </c>
-      <c r="B73" s="0" t="s">
-        <v>707</v>
-      </c>
-      <c r="C73" s="0" t="s">
+      <c r="E73" s="0" t="s">
         <v>854</v>
       </c>
-      <c r="D73" s="0" t="s">
+      <c r="F73" s="0" t="s">
         <v>855</v>
       </c>
-      <c r="E73" s="0" t="s">
+      <c r="G73" s="0" t="s">
         <v>856</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="H73" s="0" t="s">
         <v>857</v>
       </c>
-      <c r="G73" s="0" t="s">
+      <c r="I73" s="0" t="s">
+        <v>852</v>
+      </c>
+      <c r="J73" s="0" t="s">
+        <v>853</v>
+      </c>
+      <c r="K73" s="0" t="s">
+        <v>854</v>
+      </c>
+      <c r="L73" s="0" t="s">
         <v>858</v>
       </c>
-      <c r="H73" s="0" t="s">
+      <c r="M73" s="0" t="s">
         <v>859</v>
       </c>
-      <c r="I73" s="0" t="s">
-        <v>854</v>
-      </c>
-      <c r="J73" s="0" t="s">
-        <v>855</v>
-      </c>
-      <c r="K73" s="0" t="s">
-        <v>856</v>
-      </c>
-      <c r="L73" s="0" t="s">
+      <c r="N73" s="0" t="s">
         <v>860</v>
-      </c>
-      <c r="M73" s="0" t="s">
-        <v>861</v>
-      </c>
-      <c r="N73" s="0" t="s">
-        <v>862</v>
-      </c>
-      <c r="R73" s="0" t="s">
-        <v>863</v>
-      </c>
-      <c r="S73" s="0" t="s">
-        <v>864</v>
-      </c>
-      <c r="T73" s="0" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
+        <v>861</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>707</v>
+      </c>
+      <c r="C74" s="0" t="s">
+        <v>862</v>
+      </c>
+      <c r="D74" s="0" t="s">
+        <v>863</v>
+      </c>
+      <c r="E74" s="0" t="s">
+        <v>864</v>
+      </c>
+      <c r="F74" s="0" t="s">
+        <v>865</v>
+      </c>
+      <c r="G74" s="0" t="s">
         <v>866</v>
       </c>
-      <c r="B74" s="0" t="s">
-        <v>428</v>
-      </c>
-      <c r="C74" s="0" t="s">
+      <c r="H74" s="0" t="s">
         <v>867</v>
       </c>
-      <c r="D74" s="0" t="s">
+      <c r="I74" s="0" t="s">
+        <v>862</v>
+      </c>
+      <c r="J74" s="0" t="s">
+        <v>863</v>
+      </c>
+      <c r="K74" s="0" t="s">
+        <v>864</v>
+      </c>
+      <c r="L74" s="0" t="s">
         <v>868</v>
       </c>
-      <c r="E74" s="0" t="s">
+      <c r="M74" s="0" t="s">
         <v>869</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="N74" s="0" t="s">
         <v>870</v>
       </c>
-      <c r="G74" s="0" t="s">
+      <c r="R74" s="0" t="s">
         <v>871</v>
       </c>
-      <c r="H74" s="0" t="s">
+      <c r="S74" s="0" t="s">
         <v>872</v>
       </c>
-      <c r="I74" s="0" t="s">
-        <v>867</v>
-      </c>
-      <c r="J74" s="0" t="s">
-        <v>868</v>
-      </c>
-      <c r="K74" s="0" t="s">
-        <v>869</v>
-      </c>
-      <c r="L74" s="0" t="s">
+      <c r="T74" s="0" t="s">
         <v>873</v>
-      </c>
-      <c r="M74" s="0" t="s">
-        <v>874</v>
-      </c>
-      <c r="N74" s="0" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
+        <v>874</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="C75" s="0" t="s">
+        <v>875</v>
+      </c>
+      <c r="D75" s="0" t="s">
         <v>876</v>
       </c>
-      <c r="B75" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="C75" s="0" t="s">
+      <c r="E75" s="0" t="s">
         <v>877</v>
       </c>
-      <c r="D75" s="0" t="s">
+      <c r="F75" s="0" t="s">
         <v>878</v>
       </c>
-      <c r="E75" s="0" t="s">
+      <c r="G75" s="0" t="s">
         <v>879</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="H75" s="0" t="s">
         <v>880</v>
       </c>
-      <c r="G75" s="0" t="s">
+      <c r="I75" s="0" t="s">
+        <v>875</v>
+      </c>
+      <c r="J75" s="0" t="s">
+        <v>876</v>
+      </c>
+      <c r="K75" s="0" t="s">
+        <v>877</v>
+      </c>
+      <c r="L75" s="0" t="s">
         <v>881</v>
       </c>
-      <c r="H75" s="0" t="s">
+      <c r="M75" s="0" t="s">
         <v>882</v>
       </c>
-      <c r="I75" s="0" t="s">
-        <v>877</v>
-      </c>
-      <c r="J75" s="0" t="s">
-        <v>878</v>
-      </c>
-      <c r="K75" s="0" t="s">
-        <v>879</v>
-      </c>
-      <c r="L75" s="0" t="s">
+      <c r="N75" s="0" t="s">
         <v>883</v>
-      </c>
-      <c r="M75" s="0" t="s">
-        <v>884</v>
-      </c>
-      <c r="N75" s="0" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
+        <v>884</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="C76" s="0" t="s">
+        <v>885</v>
+      </c>
+      <c r="D76" s="0" t="s">
         <v>886</v>
       </c>
-      <c r="B76" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="C76" s="0" t="s">
+      <c r="E76" s="0" t="s">
         <v>887</v>
       </c>
-      <c r="D76" s="0" t="s">
+      <c r="F76" s="0" t="s">
         <v>888</v>
       </c>
-      <c r="E76" s="0" t="s">
+      <c r="G76" s="0" t="s">
         <v>889</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="H76" s="0" t="s">
         <v>890</v>
       </c>
-      <c r="G76" s="0" t="s">
+      <c r="I76" s="0" t="s">
+        <v>885</v>
+      </c>
+      <c r="J76" s="0" t="s">
+        <v>886</v>
+      </c>
+      <c r="K76" s="0" t="s">
+        <v>887</v>
+      </c>
+      <c r="L76" s="0" t="s">
         <v>891</v>
       </c>
-      <c r="H76" s="0" t="s">
+      <c r="M76" s="0" t="s">
         <v>892</v>
       </c>
-      <c r="I76" s="0" t="s">
+      <c r="N76" s="0" t="s">
         <v>893</v>
-      </c>
-      <c r="J76" s="0" t="s">
-        <v>894</v>
-      </c>
-      <c r="K76" s="0" t="s">
-        <v>895</v>
-      </c>
-      <c r="L76" s="0" t="s">
-        <v>896</v>
-      </c>
-      <c r="M76" s="0" t="s">
-        <v>897</v>
-      </c>
-      <c r="N76" s="0" t="s">
-        <v>898</v>
-      </c>
-      <c r="R76" s="0" t="s">
-        <v>899</v>
-      </c>
-      <c r="S76" s="0" t="s">
-        <v>900</v>
-      </c>
-      <c r="T76" s="0" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="B77" s="0" t="s">
         <v>139</v>
       </c>
       <c r="C77" s="0" t="s">
+        <v>895</v>
+      </c>
+      <c r="D77" s="0" t="s">
+        <v>896</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>897</v>
+      </c>
+      <c r="F77" s="0" t="s">
+        <v>898</v>
+      </c>
+      <c r="G77" s="0" t="s">
+        <v>899</v>
+      </c>
+      <c r="H77" s="0" t="s">
+        <v>900</v>
+      </c>
+      <c r="I77" s="0" t="s">
+        <v>901</v>
+      </c>
+      <c r="J77" s="0" t="s">
+        <v>902</v>
+      </c>
+      <c r="K77" s="0" t="s">
         <v>903</v>
       </c>
-      <c r="D77" s="0" t="s">
+      <c r="L77" s="0" t="s">
         <v>904</v>
       </c>
-      <c r="E77" s="0" t="s">
+      <c r="M77" s="0" t="s">
         <v>905</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="N77" s="0" t="s">
         <v>906</v>
       </c>
-      <c r="G77" s="0" t="s">
+      <c r="R77" s="0" t="s">
         <v>907</v>
       </c>
-      <c r="H77" s="0" t="s">
+      <c r="S77" s="0" t="s">
         <v>908</v>
       </c>
-      <c r="I77" s="0" t="s">
+      <c r="T77" s="0" t="s">
         <v>909</v>
-      </c>
-      <c r="J77" s="0" t="s">
-        <v>910</v>
-      </c>
-      <c r="K77" s="0" t="s">
-        <v>911</v>
-      </c>
-      <c r="L77" s="0" t="s">
-        <v>912</v>
-      </c>
-      <c r="M77" s="0" t="s">
-        <v>913</v>
-      </c>
-      <c r="N77" s="0" t="s">
-        <v>914</v>
-      </c>
-      <c r="R77" s="0" t="s">
-        <v>915</v>
-      </c>
-      <c r="S77" s="0" t="s">
-        <v>916</v>
-      </c>
-      <c r="T77" s="0" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="B78" s="0" t="s">
         <v>139</v>
       </c>
       <c r="C78" s="0" t="s">
+        <v>911</v>
+      </c>
+      <c r="D78" s="0" t="s">
+        <v>912</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>913</v>
+      </c>
+      <c r="F78" s="0" t="s">
+        <v>914</v>
+      </c>
+      <c r="G78" s="0" t="s">
+        <v>915</v>
+      </c>
+      <c r="H78" s="0" t="s">
+        <v>916</v>
+      </c>
+      <c r="I78" s="0" t="s">
+        <v>917</v>
+      </c>
+      <c r="J78" s="0" t="s">
+        <v>918</v>
+      </c>
+      <c r="K78" s="0" t="s">
         <v>919</v>
       </c>
-      <c r="D78" s="0" t="s">
+      <c r="L78" s="0" t="s">
         <v>920</v>
       </c>
-      <c r="E78" s="0" t="s">
+      <c r="M78" s="0" t="s">
         <v>921</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="N78" s="0" t="s">
         <v>922</v>
       </c>
-      <c r="G78" s="0" t="s">
+      <c r="R78" s="0" t="s">
         <v>923</v>
       </c>
-      <c r="H78" s="0" t="s">
+      <c r="S78" s="0" t="s">
         <v>924</v>
       </c>
-      <c r="I78" s="0" t="s">
-        <v>919</v>
-      </c>
-      <c r="J78" s="0" t="s">
-        <v>920</v>
-      </c>
-      <c r="K78" s="0" t="s">
-        <v>921</v>
-      </c>
-      <c r="L78" s="0" t="s">
+      <c r="T78" s="0" t="s">
         <v>925</v>
-      </c>
-      <c r="M78" s="0" t="s">
-        <v>926</v>
-      </c>
-      <c r="N78" s="0" t="s">
-        <v>927</v>
-      </c>
-      <c r="R78" s="0" t="s">
-        <v>928</v>
-      </c>
-      <c r="S78" s="0" t="s">
-        <v>929</v>
-      </c>
-      <c r="T78" s="0" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>139</v>
       </c>
       <c r="C79" s="0" t="s">
+        <v>927</v>
+      </c>
+      <c r="D79" s="0" t="s">
+        <v>928</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>929</v>
+      </c>
+      <c r="F79" s="0" t="s">
+        <v>930</v>
+      </c>
+      <c r="G79" s="0" t="s">
+        <v>931</v>
+      </c>
+      <c r="H79" s="0" t="s">
         <v>932</v>
       </c>
-      <c r="D79" s="0" t="s">
+      <c r="I79" s="0" t="s">
+        <v>927</v>
+      </c>
+      <c r="J79" s="0" t="s">
+        <v>928</v>
+      </c>
+      <c r="K79" s="0" t="s">
+        <v>929</v>
+      </c>
+      <c r="L79" s="0" t="s">
         <v>933</v>
       </c>
-      <c r="E79" s="0" t="s">
+      <c r="M79" s="0" t="s">
         <v>934</v>
       </c>
-      <c r="I79" s="0" t="s">
-        <v>932</v>
-      </c>
-      <c r="J79" s="0" t="s">
-        <v>933</v>
-      </c>
-      <c r="K79" s="0" t="s">
-        <v>934</v>
+      <c r="N79" s="0" t="s">
+        <v>935</v>
+      </c>
+      <c r="R79" s="0" t="s">
+        <v>936</v>
+      </c>
+      <c r="S79" s="0" t="s">
+        <v>937</v>
+      </c>
+      <c r="T79" s="0" t="s">
+        <v>938</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>776</v>
+        <v>139</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>938</v>
-      </c>
-      <c r="F80" s="0" t="s">
-        <v>939</v>
-      </c>
-      <c r="G80" s="0" t="s">
+        <v>942</v>
+      </c>
+      <c r="I80" s="0" t="s">
         <v>940</v>
       </c>
-      <c r="H80" s="0" t="s">
+      <c r="J80" s="0" t="s">
         <v>941</v>
       </c>
-      <c r="I80" s="0" t="s">
-        <v>936</v>
-      </c>
-      <c r="J80" s="0" t="s">
-        <v>937</v>
-      </c>
       <c r="K80" s="0" t="s">
-        <v>938</v>
-      </c>
-      <c r="L80" s="0" t="s">
         <v>942</v>
-      </c>
-      <c r="M80" s="0" t="s">
-        <v>943</v>
-      </c>
-      <c r="N80" s="0" t="s">
-        <v>944</v>
-      </c>
-      <c r="R80" s="0" t="s">
-        <v>945</v>
-      </c>
-      <c r="S80" s="0" t="s">
-        <v>946</v>
-      </c>
-      <c r="T80" s="0" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
+        <v>943</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>776</v>
+      </c>
+      <c r="C81" s="0" t="s">
+        <v>944</v>
+      </c>
+      <c r="D81" s="0" t="s">
+        <v>945</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>946</v>
+      </c>
+      <c r="F81" s="0" t="s">
+        <v>947</v>
+      </c>
+      <c r="G81" s="0" t="s">
         <v>948</v>
       </c>
-      <c r="B81" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="C81" s="0" t="s">
+      <c r="H81" s="0" t="s">
         <v>949</v>
       </c>
-      <c r="D81" s="0" t="s">
+      <c r="I81" s="0" t="s">
+        <v>944</v>
+      </c>
+      <c r="J81" s="0" t="s">
+        <v>945</v>
+      </c>
+      <c r="K81" s="0" t="s">
+        <v>946</v>
+      </c>
+      <c r="L81" s="0" t="s">
         <v>950</v>
       </c>
-      <c r="E81" s="0" t="s">
+      <c r="M81" s="0" t="s">
         <v>951</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="N81" s="0" t="s">
         <v>952</v>
       </c>
-      <c r="G81" s="0" t="s">
+      <c r="R81" s="0" t="s">
         <v>953</v>
       </c>
-      <c r="H81" s="0" t="s">
+      <c r="S81" s="0" t="s">
         <v>954</v>
       </c>
-      <c r="I81" s="0" t="s">
-        <v>949</v>
-      </c>
-      <c r="J81" s="0" t="s">
-        <v>950</v>
-      </c>
-      <c r="K81" s="0" t="s">
-        <v>951</v>
-      </c>
-      <c r="L81" s="0" t="s">
+      <c r="T81" s="0" t="s">
         <v>955</v>
-      </c>
-      <c r="M81" s="0" t="s">
-        <v>956</v>
-      </c>
-      <c r="N81" s="0" t="s">
-        <v>957</v>
-      </c>
-      <c r="R81" s="0" t="s">
-        <v>958</v>
-      </c>
-      <c r="S81" s="0" t="s">
-        <v>959</v>
-      </c>
-      <c r="T81" s="0" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
+        <v>956</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>957</v>
+      </c>
+      <c r="D82" s="0" t="s">
+        <v>958</v>
+      </c>
+      <c r="E82" s="0" t="s">
+        <v>959</v>
+      </c>
+      <c r="F82" s="0" t="s">
+        <v>960</v>
+      </c>
+      <c r="G82" s="0" t="s">
         <v>961</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="H82" s="0" t="s">
         <v>962</v>
       </c>
-      <c r="C82" s="0" t="s">
+      <c r="I82" s="0" t="s">
+        <v>957</v>
+      </c>
+      <c r="J82" s="0" t="s">
+        <v>958</v>
+      </c>
+      <c r="K82" s="0" t="s">
+        <v>959</v>
+      </c>
+      <c r="L82" s="0" t="s">
         <v>963</v>
       </c>
-      <c r="D82" s="0" t="s">
+      <c r="M82" s="0" t="s">
         <v>964</v>
       </c>
-      <c r="E82" s="0" t="s">
+      <c r="N82" s="0" t="s">
         <v>965</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="R82" s="0" t="s">
         <v>966</v>
       </c>
-      <c r="G82" s="0" t="s">
+      <c r="S82" s="0" t="s">
         <v>967</v>
       </c>
-      <c r="H82" s="0" t="s">
+      <c r="T82" s="0" t="s">
         <v>968</v>
-      </c>
-      <c r="I82" s="0" t="s">
-        <v>969</v>
-      </c>
-      <c r="J82" s="0" t="s">
-        <v>970</v>
-      </c>
-      <c r="K82" s="0" t="s">
-        <v>971</v>
-      </c>
-      <c r="L82" s="0" t="s">
-        <v>972</v>
-      </c>
-      <c r="M82" s="0" t="s">
-        <v>973</v>
-      </c>
-      <c r="N82" s="0" t="s">
-        <v>974</v>
-      </c>
-      <c r="R82" s="0" t="s">
-        <v>975</v>
-      </c>
-      <c r="S82" s="0" t="s">
-        <v>976</v>
-      </c>
-      <c r="T82" s="0" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
+        <v>969</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>970</v>
+      </c>
+      <c r="C83" s="0" t="s">
+        <v>971</v>
+      </c>
+      <c r="D83" s="0" t="s">
+        <v>972</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>973</v>
+      </c>
+      <c r="F83" s="0" t="s">
+        <v>974</v>
+      </c>
+      <c r="G83" s="0" t="s">
+        <v>975</v>
+      </c>
+      <c r="H83" s="0" t="s">
+        <v>976</v>
+      </c>
+      <c r="I83" s="0" t="s">
+        <v>977</v>
+      </c>
+      <c r="J83" s="0" t="s">
         <v>978</v>
       </c>
-      <c r="B83" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="C83" s="0" t="s">
+      <c r="K83" s="0" t="s">
         <v>979</v>
       </c>
-      <c r="D83" s="0" t="s">
+      <c r="L83" s="0" t="s">
         <v>980</v>
       </c>
-      <c r="E83" s="0" t="s">
+      <c r="M83" s="0" t="s">
         <v>981</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="N83" s="0" t="s">
         <v>982</v>
       </c>
-      <c r="G83" s="0" t="s">
+      <c r="R83" s="0" t="s">
         <v>983</v>
       </c>
-      <c r="H83" s="0" t="s">
+      <c r="S83" s="0" t="s">
         <v>984</v>
       </c>
-      <c r="I83" s="0" t="s">
-        <v>979</v>
-      </c>
-      <c r="J83" s="0" t="s">
+      <c r="T83" s="0" t="s">
         <v>985</v>
-      </c>
-      <c r="K83" s="0" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7966,34 +7990,34 @@
         <v>986</v>
       </c>
       <c r="B84" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="C84" s="0" t="s">
         <v>987</v>
       </c>
-      <c r="C84" s="0" t="s">
+      <c r="D84" s="0" t="s">
         <v>988</v>
       </c>
-      <c r="D84" s="0" t="s">
+      <c r="E84" s="0" t="s">
         <v>989</v>
       </c>
-      <c r="E84" s="0" t="s">
+      <c r="F84" s="0" t="s">
         <v>990</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="G84" s="0" t="s">
         <v>991</v>
       </c>
-      <c r="G84" s="0" t="s">
+      <c r="H84" s="0" t="s">
         <v>992</v>
       </c>
-      <c r="H84" s="0" t="s">
+      <c r="I84" s="0" t="s">
+        <v>987</v>
+      </c>
+      <c r="J84" s="0" t="s">
         <v>993</v>
       </c>
-      <c r="I84" s="0" t="s">
-        <v>988</v>
-      </c>
-      <c r="J84" s="0" t="s">
+      <c r="K84" s="0" t="s">
         <v>989</v>
-      </c>
-      <c r="K84" s="0" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8001,595 +8025,595 @@
         <v>994</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>139</v>
+        <v>995</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D85" s="0" t="s">
+        <v>997</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>998</v>
+      </c>
+      <c r="F85" s="0" t="s">
+        <v>999</v>
+      </c>
+      <c r="G85" s="0" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H85" s="0" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I85" s="0" t="s">
         <v>996</v>
       </c>
-      <c r="E85" s="0" t="s">
+      <c r="J85" s="0" t="s">
         <v>997</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="K85" s="0" t="s">
         <v>998</v>
-      </c>
-      <c r="G85" s="0" t="s">
-        <v>999</v>
-      </c>
-      <c r="H85" s="0" t="s">
-        <v>1000</v>
-      </c>
-      <c r="I85" s="0" t="s">
-        <v>995</v>
-      </c>
-      <c r="J85" s="0" t="s">
-        <v>996</v>
-      </c>
-      <c r="K85" s="0" t="s">
-        <v>997</v>
-      </c>
-      <c r="L85" s="0" t="s">
-        <v>1001</v>
-      </c>
-      <c r="M85" s="0" t="s">
-        <v>1002</v>
-      </c>
-      <c r="N85" s="0" t="s">
-        <v>1003</v>
-      </c>
-      <c r="R85" s="0" t="s">
-        <v>1004</v>
-      </c>
-      <c r="S85" s="0" t="s">
-        <v>1005</v>
-      </c>
-      <c r="T85" s="0" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="C86" s="0" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D86" s="0" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F86" s="0" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G86" s="0" t="s">
         <v>1007</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="H86" s="0" t="s">
         <v>1008</v>
       </c>
-      <c r="C86" s="0" t="s">
+      <c r="I86" s="0" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J86" s="0" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K86" s="0" t="s">
+        <v>1005</v>
+      </c>
+      <c r="L86" s="0" t="s">
         <v>1009</v>
       </c>
-      <c r="D86" s="0" t="s">
+      <c r="M86" s="0" t="s">
         <v>1010</v>
       </c>
-      <c r="E86" s="0" t="s">
+      <c r="N86" s="0" t="s">
         <v>1011</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="R86" s="0" t="s">
         <v>1012</v>
       </c>
-      <c r="G86" s="0" t="s">
+      <c r="S86" s="0" t="s">
         <v>1013</v>
       </c>
-      <c r="H86" s="0" t="s">
+      <c r="T86" s="0" t="s">
         <v>1014</v>
-      </c>
-      <c r="I86" s="0" t="s">
-        <v>1015</v>
-      </c>
-      <c r="J86" s="0" t="s">
-        <v>1016</v>
-      </c>
-      <c r="K86" s="0" t="s">
-        <v>1017</v>
-      </c>
-      <c r="L86" s="0" t="s">
-        <v>1018</v>
-      </c>
-      <c r="M86" s="0" t="s">
-        <v>1019</v>
-      </c>
-      <c r="N86" s="0" t="s">
-        <v>1020</v>
-      </c>
-      <c r="R86" s="0" t="s">
-        <v>1021</v>
-      </c>
-      <c r="S86" s="0" t="s">
-        <v>1022</v>
-      </c>
-      <c r="T86" s="0" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C87" s="0" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D87" s="0" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F87" s="0" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G87" s="0" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H87" s="0" t="s">
+        <v>1022</v>
+      </c>
+      <c r="I87" s="0" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J87" s="0" t="s">
         <v>1024</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="K87" s="0" t="s">
+        <v>1025</v>
+      </c>
+      <c r="L87" s="0" t="s">
+        <v>1026</v>
+      </c>
+      <c r="M87" s="0" t="s">
+        <v>1027</v>
+      </c>
+      <c r="N87" s="0" t="s">
+        <v>1028</v>
+      </c>
+      <c r="R87" s="0" t="s">
+        <v>1029</v>
+      </c>
+      <c r="S87" s="0" t="s">
+        <v>1030</v>
+      </c>
+      <c r="T87" s="0" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B88" s="0" t="s">
         <v>721</v>
       </c>
-      <c r="C87" s="0" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D87" s="0" t="s">
-        <v>1026</v>
-      </c>
-      <c r="E87" s="0" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F87" s="0" t="s">
-        <v>1028</v>
-      </c>
-      <c r="G87" s="0" t="s">
-        <v>1029</v>
-      </c>
-      <c r="H87" s="0" t="s">
-        <v>1030</v>
-      </c>
-      <c r="I87" s="0" t="s">
-        <v>1025</v>
-      </c>
-      <c r="J87" s="0" t="s">
-        <v>1026</v>
-      </c>
-      <c r="K87" s="0" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B88" s="0" t="s">
-        <v>139</v>
-      </c>
       <c r="C88" s="0" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D88" s="0" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E88" s="0" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F88" s="0" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G88" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H88" s="0" t="s">
+        <v>1038</v>
+      </c>
+      <c r="I88" s="0" t="s">
         <v>1033</v>
       </c>
-      <c r="E88" s="0" t="s">
+      <c r="J88" s="0" t="s">
         <v>1034</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="K88" s="0" t="s">
         <v>1035</v>
       </c>
-      <c r="G88" s="0" t="s">
-        <v>1036</v>
-      </c>
-      <c r="H88" s="0" t="s">
-        <v>1037</v>
-      </c>
-      <c r="I88" s="0" t="s">
-        <v>1038</v>
-      </c>
-      <c r="J88" s="0" t="s">
+    </row>
+    <row r="89" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="s">
         <v>1039</v>
-      </c>
-      <c r="K88" s="0" t="s">
-        <v>1040</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="M88" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="N88" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="O88" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="P88" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="Q88" s="2" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
-        <v>1047</v>
       </c>
       <c r="B89" s="0" t="s">
         <v>139</v>
       </c>
       <c r="C89" s="0" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E89" s="0" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F89" s="0" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G89" s="0" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H89" s="0" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I89" s="0" t="s">
+        <v>1046</v>
+      </c>
+      <c r="J89" s="0" t="s">
+        <v>1047</v>
+      </c>
+      <c r="K89" s="0" t="s">
         <v>1048</v>
       </c>
-      <c r="D89" s="0" t="s">
+      <c r="L89" s="2" t="s">
         <v>1049</v>
       </c>
-      <c r="E89" s="0" t="s">
+      <c r="M89" s="2" t="s">
         <v>1050</v>
       </c>
-      <c r="F89" s="0" t="s">
+      <c r="N89" s="2" t="s">
         <v>1051</v>
       </c>
-      <c r="G89" s="0" t="s">
+      <c r="O89" s="2" t="s">
         <v>1052</v>
       </c>
-      <c r="H89" s="0" t="s">
+      <c r="P89" s="2" t="s">
         <v>1053</v>
       </c>
-      <c r="I89" s="0" t="s">
+      <c r="Q89" s="2" t="s">
         <v>1054</v>
-      </c>
-      <c r="J89" s="0" t="s">
-        <v>1055</v>
-      </c>
-      <c r="K89" s="0" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B90" s="0" t="s">
         <v>139</v>
       </c>
       <c r="C90" s="0" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E90" s="0" t="s">
         <v>1058</v>
       </c>
-      <c r="D90" s="0" t="s">
-        <v>283</v>
-      </c>
-      <c r="E90" s="0" t="s">
+      <c r="F90" s="0" t="s">
         <v>1059</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="G90" s="0" t="s">
         <v>1060</v>
       </c>
-      <c r="G90" s="0" t="s">
+      <c r="H90" s="0" t="s">
         <v>1061</v>
       </c>
-      <c r="H90" s="0" t="s">
+      <c r="I90" s="0" t="s">
         <v>1062</v>
       </c>
-      <c r="I90" s="0" t="s">
-        <v>780</v>
-      </c>
       <c r="J90" s="0" t="s">
-        <v>780</v>
+        <v>1063</v>
       </c>
       <c r="K90" s="0" t="s">
-        <v>780</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B91" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F91" s="0" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G91" s="0" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H91" s="0" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I91" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="J91" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="K91" s="0" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B92" s="0" t="s">
         <v>376</v>
       </c>
-      <c r="C91" s="0" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D91" s="0" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E91" s="0" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F91" s="0" t="s">
-        <v>1067</v>
-      </c>
-      <c r="G91" s="0" t="s">
-        <v>1068</v>
-      </c>
-      <c r="H91" s="0" t="s">
-        <v>1069</v>
-      </c>
-      <c r="I91" s="0" t="s">
-        <v>1070</v>
-      </c>
-      <c r="J91" s="0" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K91" s="0" t="s">
+      <c r="C92" s="0" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="92" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="D92" s="0" t="s">
         <v>1073</v>
       </c>
-      <c r="B92" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="C92" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="D92" s="0" t="s">
-        <v>203</v>
-      </c>
       <c r="E92" s="0" t="s">
-        <v>204</v>
+        <v>1074</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="I92" s="0" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="J92" s="0" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="K92" s="0" t="s">
-        <v>1079</v>
-      </c>
-      <c r="L92" s="2" t="s">
         <v>1080</v>
       </c>
-      <c r="M92" s="2" t="s">
+    </row>
+    <row r="93" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="s">
         <v>1081</v>
-      </c>
-      <c r="N92" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="O92" s="0" t="s">
-        <v>1083</v>
-      </c>
-      <c r="P92" s="0" t="s">
-        <v>1084</v>
-      </c>
-      <c r="Q92" s="0" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
-        <v>1086</v>
       </c>
       <c r="B93" s="0" t="s">
         <v>139</v>
       </c>
       <c r="C93" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="E93" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="F93" s="0" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G93" s="0" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H93" s="0" t="s">
+        <v>1084</v>
+      </c>
+      <c r="I93" s="0" t="s">
+        <v>1085</v>
+      </c>
+      <c r="J93" s="0" t="s">
+        <v>1086</v>
+      </c>
+      <c r="K93" s="0" t="s">
         <v>1087</v>
       </c>
-      <c r="D93" s="0" t="s">
+      <c r="L93" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="E93" s="0" t="s">
+      <c r="M93" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="I93" s="0" t="s">
+      <c r="N93" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="J93" s="0" t="s">
+      <c r="O93" s="0" t="s">
         <v>1091</v>
       </c>
-      <c r="K93" s="0" t="s">
+      <c r="P93" s="0" t="s">
         <v>1092</v>
+      </c>
+      <c r="Q93" s="0" t="s">
+        <v>1093</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B94" s="0" t="s">
         <v>139</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="I94" s="0" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="J94" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="K94" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B95" s="0" t="s">
         <v>139</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F95" s="0" t="s">
         <v>1104</v>
       </c>
-      <c r="G95" s="0" t="s">
+      <c r="I95" s="0" t="s">
         <v>1105</v>
       </c>
-      <c r="H95" s="0" t="s">
+      <c r="J95" s="0" t="s">
         <v>1106</v>
       </c>
-      <c r="I95" s="0" t="s">
+      <c r="K95" s="0" t="s">
         <v>1107</v>
-      </c>
-      <c r="J95" s="0" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K95" s="0" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>139</v>
       </c>
       <c r="C96" s="0" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D96" s="0" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E96" s="0" t="s">
         <v>1111</v>
       </c>
-      <c r="D96" s="0" t="s">
+      <c r="F96" s="0" t="s">
         <v>1112</v>
       </c>
-      <c r="E96" s="0" t="s">
+      <c r="G96" s="0" t="s">
         <v>1113</v>
+      </c>
+      <c r="H96" s="0" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I96" s="0" t="s">
+        <v>1115</v>
+      </c>
+      <c r="J96" s="0" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K96" s="0" t="s">
+        <v>1117</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>139</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>1117</v>
-      </c>
-      <c r="I97" s="0" t="s">
-        <v>1118</v>
-      </c>
-      <c r="J97" s="0" t="s">
-        <v>1119</v>
-      </c>
-      <c r="K97" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>376</v>
+        <v>139</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>1087</v>
+        <v>1123</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>1088</v>
+        <v>1124</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>1089</v>
+        <v>1125</v>
       </c>
       <c r="I98" s="0" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="J98" s="0" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="K98" s="0" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>1126</v>
+        <v>376</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>1127</v>
+        <v>1095</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>1128</v>
+        <v>1096</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F99" s="0" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I99" s="0" t="s">
         <v>1130</v>
       </c>
-      <c r="G99" s="0" t="s">
+      <c r="J99" s="0" t="s">
         <v>1131</v>
       </c>
-      <c r="H99" s="0" t="s">
+      <c r="K99" s="0" t="s">
         <v>1132</v>
-      </c>
-      <c r="I99" s="0" t="s">
-        <v>1127</v>
-      </c>
-      <c r="J99" s="0" t="s">
-        <v>1128</v>
-      </c>
-      <c r="K99" s="0" t="s">
-        <v>1129</v>
-      </c>
-      <c r="L99" s="0" t="s">
-        <v>1133</v>
-      </c>
-      <c r="M99" s="0" t="s">
-        <v>1134</v>
-      </c>
-      <c r="N99" s="0" t="s">
-        <v>1135</v>
-      </c>
-      <c r="R99" s="0" t="s">
-        <v>863</v>
-      </c>
-      <c r="S99" s="0" t="s">
-        <v>864</v>
-      </c>
-      <c r="T99" s="0" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D100" s="0" t="s">
         <v>1136</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="E100" s="0" t="s">
         <v>1137</v>
       </c>
-      <c r="C100" s="0" t="s">
+      <c r="F100" s="0" t="s">
         <v>1138</v>
       </c>
-      <c r="D100" s="0" t="s">
+      <c r="G100" s="0" t="s">
         <v>1139</v>
       </c>
-      <c r="E100" s="0" t="s">
+      <c r="H100" s="0" t="s">
         <v>1140</v>
       </c>
-      <c r="F100" s="0" t="s">
+      <c r="I100" s="0" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J100" s="0" t="s">
+        <v>1136</v>
+      </c>
+      <c r="K100" s="0" t="s">
+        <v>1137</v>
+      </c>
+      <c r="L100" s="0" t="s">
         <v>1141</v>
       </c>
-      <c r="G100" s="0" t="s">
+      <c r="M100" s="0" t="s">
         <v>1142</v>
       </c>
-      <c r="H100" s="0" t="s">
+      <c r="N100" s="0" t="s">
         <v>1143</v>
       </c>
-      <c r="I100" s="0" t="s">
-        <v>1138</v>
-      </c>
-      <c r="J100" s="0" t="s">
-        <v>1139</v>
-      </c>
-      <c r="K100" s="0" t="s">
-        <v>1140</v>
+      <c r="R100" s="0" t="s">
+        <v>871</v>
+      </c>
+      <c r="S100" s="0" t="s">
+        <v>872</v>
+      </c>
+      <c r="T100" s="0" t="s">
+        <v>873</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8617,119 +8641,110 @@
       <c r="H101" s="0" t="s">
         <v>1151</v>
       </c>
-      <c r="L101" s="0" t="s">
-        <v>1152</v>
-      </c>
-      <c r="M101" s="0" t="s">
-        <v>1153</v>
-      </c>
-      <c r="N101" s="0" t="s">
-        <v>1154</v>
-      </c>
-      <c r="R101" s="0" t="s">
-        <v>1155</v>
-      </c>
-      <c r="S101" s="0" t="s">
-        <v>1156</v>
-      </c>
-      <c r="T101" s="0" t="s">
-        <v>1157</v>
+      <c r="I101" s="0" t="s">
+        <v>1146</v>
+      </c>
+      <c r="J101" s="0" t="s">
+        <v>1147</v>
+      </c>
+      <c r="K101" s="0" t="s">
+        <v>1148</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F102" s="0" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G102" s="0" t="s">
         <v>1158</v>
       </c>
-      <c r="B102" s="0" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C102" s="0" t="s">
+      <c r="H102" s="0" t="s">
         <v>1159</v>
       </c>
-      <c r="D102" s="0" t="s">
+      <c r="L102" s="0" t="s">
         <v>1160</v>
       </c>
-      <c r="E102" s="0" t="s">
+      <c r="M102" s="0" t="s">
         <v>1161</v>
       </c>
-      <c r="F102" s="0" t="s">
+      <c r="N102" s="0" t="s">
         <v>1162</v>
       </c>
-      <c r="G102" s="0" t="s">
+      <c r="R102" s="0" t="s">
         <v>1163</v>
       </c>
-      <c r="H102" s="0" t="s">
+      <c r="S102" s="0" t="s">
         <v>1164</v>
       </c>
-      <c r="L102" s="0" t="s">
+      <c r="T102" s="0" t="s">
         <v>1165</v>
-      </c>
-      <c r="M102" s="0" t="s">
-        <v>1166</v>
-      </c>
-      <c r="N102" s="0" t="s">
-        <v>1167</v>
-      </c>
-      <c r="R102" s="0" t="s">
-        <v>1155</v>
-      </c>
-      <c r="S102" s="0" t="s">
-        <v>1156</v>
-      </c>
-      <c r="T102" s="0" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D103" s="0" t="s">
         <v>1168</v>
       </c>
-      <c r="B103" s="0" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C103" s="0" t="s">
+      <c r="E103" s="0" t="s">
         <v>1169</v>
       </c>
-      <c r="D103" s="0" t="s">
+      <c r="F103" s="0" t="s">
         <v>1170</v>
       </c>
-      <c r="E103" s="0" t="s">
+      <c r="G103" s="0" t="s">
         <v>1171</v>
       </c>
-      <c r="F103" s="0" t="s">
+      <c r="H103" s="0" t="s">
         <v>1172</v>
       </c>
-      <c r="G103" s="0" t="s">
+      <c r="L103" s="0" t="s">
         <v>1173</v>
       </c>
-      <c r="H103" s="0" t="s">
+      <c r="M103" s="0" t="s">
         <v>1174</v>
       </c>
-      <c r="L103" s="0" t="s">
+      <c r="N103" s="0" t="s">
+        <v>1175</v>
+      </c>
+      <c r="R103" s="0" t="s">
+        <v>1163</v>
+      </c>
+      <c r="S103" s="0" t="s">
+        <v>1164</v>
+      </c>
+      <c r="T103" s="0" t="s">
         <v>1165</v>
-      </c>
-      <c r="M103" s="0" t="s">
-        <v>1166</v>
-      </c>
-      <c r="N103" s="0" t="s">
-        <v>1167</v>
-      </c>
-      <c r="R103" s="0" t="s">
-        <v>1155</v>
-      </c>
-      <c r="S103" s="0" t="s">
-        <v>1156</v>
-      </c>
-      <c r="T103" s="0" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>1176</v>
+        <v>1153</v>
       </c>
       <c r="C104" s="0" t="s">
         <v>1177</v>
@@ -8750,66 +8765,110 @@
         <v>1182</v>
       </c>
       <c r="L104" s="0" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="M104" s="0" t="s">
-        <v>1184</v>
+        <v>1174</v>
       </c>
       <c r="N104" s="0" t="s">
-        <v>1185</v>
+        <v>1175</v>
       </c>
       <c r="R104" s="0" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="S104" s="0" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="T104" s="0" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D105" s="0" t="s">
         <v>1186</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="E105" s="0" t="s">
         <v>1187</v>
       </c>
-      <c r="C105" s="0" t="s">
+      <c r="F105" s="0" t="s">
         <v>1188</v>
       </c>
-      <c r="D105" s="0" t="s">
+      <c r="G105" s="0" t="s">
         <v>1189</v>
       </c>
-      <c r="E105" s="0" t="s">
+      <c r="H105" s="0" t="s">
         <v>1190</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="L105" s="0" t="s">
         <v>1191</v>
       </c>
-      <c r="G105" s="0" t="s">
+      <c r="M105" s="0" t="s">
         <v>1192</v>
       </c>
-      <c r="H105" s="0" t="s">
+      <c r="N105" s="0" t="s">
         <v>1193</v>
       </c>
-      <c r="L105" s="0" t="s">
+      <c r="R105" s="0" t="s">
+        <v>1163</v>
+      </c>
+      <c r="S105" s="0" t="s">
+        <v>1164</v>
+      </c>
+      <c r="T105" s="0" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="s">
         <v>1194</v>
       </c>
-      <c r="M105" s="0" t="s">
+      <c r="B106" s="0" t="s">
         <v>1195</v>
       </c>
-      <c r="N105" s="0" t="s">
+      <c r="C106" s="0" t="s">
         <v>1196</v>
       </c>
-      <c r="R105" s="0" t="s">
-        <v>1155</v>
-      </c>
-      <c r="S105" s="0" t="s">
-        <v>1156</v>
-      </c>
-      <c r="T105" s="0" t="s">
-        <v>1157</v>
+      <c r="D106" s="0" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F106" s="0" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G106" s="0" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H106" s="0" t="s">
+        <v>1201</v>
+      </c>
+      <c r="L106" s="0" t="s">
+        <v>1202</v>
+      </c>
+      <c r="M106" s="0" t="s">
+        <v>1203</v>
+      </c>
+      <c r="N106" s="0" t="s">
+        <v>1204</v>
+      </c>
+      <c r="R106" s="0" t="s">
+        <v>1163</v>
+      </c>
+      <c r="S106" s="0" t="s">
+        <v>1164</v>
+      </c>
+      <c r="T106" s="0" t="s">
+        <v>1165</v>
       </c>
     </row>
   </sheetData>
